--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/Invoice_10.11651202.1_1405_05_26.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/Invoice_10.11651202.1_1405_05_26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756E6DD6-D264-4F1F-A1FB-8D20F16E117C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403ACE41-317E-4600-84B4-BD02D327F1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -443,7 +443,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -492,6 +492,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -520,7 +526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -537,12 +543,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -596,11 +596,59 @@
     <xf numFmtId="3" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -931,7 +979,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I46"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -946,30 +994,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -2219,17 +2267,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2258,7 +2306,7 @@
     <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="12.5703125" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="53.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="53.28515625" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2286,1671 +2334,1681 @@
       <c r="H1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="14" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="7">
         <v>995</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="8">
         <v>0.54673611111111109</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="9">
         <v>5500000</v>
       </c>
-      <c r="G2" s="9">
-        <v>0</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9">
         <v>102612762</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="17"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="15"/>
     </row>
     <row r="3" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10">
         <v>995</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="11">
         <v>0.83630787037037035</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <v>12200</v>
       </c>
-      <c r="G3" s="12">
-        <v>0</v>
-      </c>
-      <c r="H3" s="14">
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="12">
         <v>102600562</v>
       </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="23">
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="21">
         <v>223</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="21">
         <v>291</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="21">
         <v>12200</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>995</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="11">
         <v>0.83630787037037035</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="22">
         <v>13962200</v>
       </c>
-      <c r="G4" s="12">
-        <v>0</v>
-      </c>
-      <c r="H4" s="14">
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12">
         <v>88638362</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="21">
         <v>225</v>
       </c>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="23">
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="21">
         <v>293</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="15" t="s">
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="13" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>995</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="11">
         <v>0.99164351851851851</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <v>9000</v>
       </c>
-      <c r="G5" s="12">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14">
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12">
         <v>88629362</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="23">
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="21">
         <v>224</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="21">
         <v>292</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="21">
         <v>9000</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>995</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="11">
         <v>0.99164351851851851</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="22">
         <v>2756326</v>
       </c>
-      <c r="G6" s="12">
-        <v>0</v>
-      </c>
-      <c r="H6" s="14">
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
         <v>85873036</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="21">
         <v>226</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="23">
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="21">
         <v>294</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="15" t="s">
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="10">
         <v>995</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>0.99300925925925931</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <v>9000</v>
       </c>
-      <c r="G7" s="12">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14">
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12">
         <v>85864036</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="23">
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="21">
         <v>223</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="21">
         <v>291</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="21">
         <v>9000</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="P7" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>995</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <v>0.99300925925925931</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="22">
         <v>1600000</v>
       </c>
-      <c r="G8" s="12">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14">
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
         <v>84264036</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="21">
         <v>227</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="23">
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="21">
         <v>295</v>
       </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="15" t="s">
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="10">
         <v>995</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>0.52793981481481478</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="22">
         <v>16480000</v>
       </c>
-      <c r="G9" s="12">
-        <v>0</v>
-      </c>
-      <c r="H9" s="14">
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12">
         <v>67784036</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="21">
         <v>228</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="23">
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="21">
         <v>296</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="15" t="s">
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="10">
         <v>995</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="11">
         <v>0.47221064814814817</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="22">
         <v>7400000</v>
       </c>
-      <c r="G10" s="12">
-        <v>0</v>
-      </c>
-      <c r="H10" s="14">
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
         <v>60384036</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="21">
         <v>229</v>
       </c>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="23">
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="21">
+        <v>324</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10">
+        <v>995</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0.72593750000000001</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="22">
+        <v>18600</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12">
+        <v>60365436</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="21">
+        <v>223</v>
+      </c>
+      <c r="N11" s="21">
+        <v>291</v>
+      </c>
+      <c r="O11" s="21">
+        <v>18600</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10">
+        <v>995</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.72593750000000001</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="22">
+        <v>39318600</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>21046836</v>
+      </c>
+      <c r="I12" s="21">
+        <v>231</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="21">
+        <v>298</v>
+      </c>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10">
+        <v>995</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0.78163194444444439</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="22">
+        <v>9000</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>21037836</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="21">
+        <v>223</v>
+      </c>
+      <c r="N13" s="21">
+        <v>291</v>
+      </c>
+      <c r="O13" s="21">
+        <v>9000</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="10">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10">
+        <v>995</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="11">
+        <v>0.78163194444444439</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="22">
+        <v>4000000</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>17037836</v>
+      </c>
+      <c r="I14" s="21">
+        <v>230</v>
+      </c>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="21">
+        <v>297</v>
+      </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10">
+        <v>995</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="11">
+        <v>0.81062500000000004</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
+        <v>21275000</v>
+      </c>
+      <c r="H15" s="12">
+        <v>38312836</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="21">
+        <v>160</v>
+      </c>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="13"/>
+    </row>
+    <row r="16" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="10">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10">
+        <v>995</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="11">
+        <v>0.4157986111111111</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="22">
+        <v>2756000</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>35556836</v>
+      </c>
+      <c r="I16" s="21">
+        <v>232</v>
+      </c>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="21">
+        <v>299</v>
+      </c>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10">
+        <v>995</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="11">
+        <v>0.42410879629629628</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="22">
+        <v>1400000</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <v>34156836</v>
+      </c>
+      <c r="I17" s="21">
+        <v>233</v>
+      </c>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="21">
+        <v>300</v>
+      </c>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="10">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10">
+        <v>1</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0.59675925925925921</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="10">
+        <v>0</v>
+      </c>
+      <c r="G18" s="22">
+        <v>100000000</v>
+      </c>
+      <c r="H18" s="12">
+        <v>134156836</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="21">
+        <v>166</v>
+      </c>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="13"/>
+    </row>
+    <row r="19" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="10">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10">
+        <v>995</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="11">
+        <v>0.45131944444444444</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="22">
+        <v>9000</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12">
+        <v>134147836</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="21">
+        <v>223</v>
+      </c>
+      <c r="N19" s="21">
+        <v>291</v>
+      </c>
+      <c r="O19" s="21">
+        <v>9000</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="10">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10">
+        <v>995</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="11">
+        <v>0.45131944444444444</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="22">
+        <v>1430000</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12">
+        <v>132717836</v>
+      </c>
+      <c r="I20" s="21">
+        <v>234</v>
+      </c>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="21">
+        <v>301</v>
+      </c>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="10">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10">
+        <v>995</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="11">
+        <v>0.45287037037037037</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="22">
+        <v>28200</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12">
+        <v>132689636</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="21">
+        <v>223</v>
+      </c>
+      <c r="N21" s="21">
+        <v>291</v>
+      </c>
+      <c r="O21" s="21">
+        <v>28200</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="10">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10">
+        <v>995</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="11">
+        <v>0.45287037037037037</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="22">
+        <v>64500000</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0</v>
+      </c>
+      <c r="H22" s="12">
+        <v>68189636</v>
+      </c>
+      <c r="I22" s="21">
+        <v>235</v>
+      </c>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="21">
+        <v>302</v>
+      </c>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="10">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10">
+        <v>995</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="11">
+        <v>0.46592592592592591</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="22">
+        <v>105000</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12">
+        <v>68084636</v>
+      </c>
+      <c r="I23" s="21">
+        <v>236</v>
+      </c>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="21">
+        <v>303</v>
+      </c>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="10">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10">
+        <v>995</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="11">
+        <v>0.58806712962962959</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="22">
+        <v>3100000</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12">
+        <v>64984636</v>
+      </c>
+      <c r="I24" s="21">
+        <v>237</v>
+      </c>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="21">
+        <v>304</v>
+      </c>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="10">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10">
+        <v>995</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="11">
+        <v>0.46016203703703706</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="12">
+        <v>13000000</v>
+      </c>
+      <c r="G25" s="10">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12">
+        <v>51984636</v>
+      </c>
+      <c r="I25" s="26"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="10">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10">
+        <v>995</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="11">
+        <v>0.73033564814814811</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="22">
+        <v>2756000</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12">
+        <v>49228636</v>
+      </c>
+      <c r="I26" s="21">
+        <v>232</v>
+      </c>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="21">
+        <v>299</v>
+      </c>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="10">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10">
+        <v>1</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="11">
+        <v>0.5465740740740741</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="10">
+        <v>0</v>
+      </c>
+      <c r="G27" s="22">
+        <v>100000000</v>
+      </c>
+      <c r="H27" s="12">
+        <v>149228636</v>
+      </c>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="21">
+        <v>186</v>
+      </c>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="13"/>
+    </row>
+    <row r="28" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="10">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10">
+        <v>995</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="11">
+        <v>0.42841435185185184</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="22">
+        <v>16520000</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12">
+        <v>132708636</v>
+      </c>
+      <c r="I28" s="21">
+        <v>228</v>
+      </c>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="21">
         <v>296</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="15" t="s">
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="10">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10">
+        <v>995</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="11">
+        <v>0.71627314814814813</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="22">
+        <v>2756000</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12">
+        <v>129952636</v>
+      </c>
+      <c r="I29" s="21">
+        <v>232</v>
+      </c>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="21">
+        <v>299</v>
+      </c>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="17">
+        <v>29</v>
+      </c>
+      <c r="B30" s="17">
+        <v>995</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="18">
+        <v>0.71671296296296294</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="19">
+        <v>2756000</v>
+      </c>
+      <c r="G30" s="17">
+        <v>0</v>
+      </c>
+      <c r="H30" s="19">
+        <v>127196636</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="17">
+        <v>30</v>
+      </c>
+      <c r="B31" s="17">
+        <v>995</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="18">
+        <v>0.71753472222222225</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="17">
+        <v>0</v>
+      </c>
+      <c r="G31" s="19">
+        <v>2756000</v>
+      </c>
+      <c r="H31" s="19">
+        <v>129952636</v>
+      </c>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="10">
+        <v>31</v>
+      </c>
+      <c r="B32" s="10">
+        <v>995</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="11">
+        <v>0.39391203703703703</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="22">
+        <v>31400</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12">
+        <v>129921236</v>
+      </c>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="21">
+        <v>223</v>
+      </c>
+      <c r="N32" s="21">
+        <v>291</v>
+      </c>
+      <c r="O32" s="21">
+        <v>31400</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="10">
+        <v>32</v>
+      </c>
+      <c r="B33" s="10">
+        <v>995</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="11">
+        <v>0.39391203703703703</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="12">
+        <v>80000000</v>
+      </c>
+      <c r="G33" s="10">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12">
+        <v>49921236</v>
+      </c>
+      <c r="I33" s="26"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="10">
+        <v>33</v>
+      </c>
+      <c r="B34" s="10">
+        <v>10</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="11">
+        <v>0.38908564814814817</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="12">
+        <v>50340</v>
+      </c>
+      <c r="G34" s="10">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12">
+        <v>49870896</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="21">
+        <v>223</v>
+      </c>
+      <c r="N34" s="21">
+        <v>291</v>
+      </c>
+      <c r="O34" s="21">
+        <v>50340</v>
+      </c>
+      <c r="P34" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="10">
+        <v>34</v>
+      </c>
+      <c r="B35" s="10">
+        <v>995</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="11">
+        <v>0.39223379629629629</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="12">
+        <v>3500000</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12">
+        <v>46370896</v>
+      </c>
+      <c r="I35" s="26"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="10">
+        <v>35</v>
+      </c>
+      <c r="B36" s="10">
+        <v>995</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="11">
+        <v>0.77943287037037035</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="22">
+        <v>9000</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12">
+        <v>46361896</v>
+      </c>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="21">
+        <v>223</v>
+      </c>
+      <c r="N36" s="21">
+        <v>291</v>
+      </c>
+      <c r="O36" s="21">
+        <v>9000</v>
+      </c>
+      <c r="P36" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="10">
+        <v>36</v>
+      </c>
+      <c r="B37" s="10">
+        <v>995</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="11">
+        <v>0.77943287037037035</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" s="22">
+        <v>4000000</v>
+      </c>
+      <c r="G37" s="10">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12">
+        <v>42361896</v>
+      </c>
+      <c r="I37" s="21">
+        <v>230</v>
+      </c>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="21">
+        <v>297</v>
+      </c>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="10">
+        <v>37</v>
+      </c>
+      <c r="B38" s="10">
+        <v>995</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="11">
+        <v>0.81400462962962961</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" s="22">
+        <v>21500000</v>
+      </c>
+      <c r="G38" s="10">
+        <v>0</v>
+      </c>
+      <c r="H38" s="12">
+        <v>20861896</v>
+      </c>
+      <c r="I38" s="21">
+        <v>229</v>
+      </c>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="21">
+        <v>324</v>
+      </c>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="13" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="12">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12">
+    <row r="39" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="10">
+        <v>38</v>
+      </c>
+      <c r="B39" s="10">
+        <v>1</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="11">
+        <v>0.46181712962962962</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39" s="10">
+        <v>0</v>
+      </c>
+      <c r="G39" s="22">
+        <v>88000000</v>
+      </c>
+      <c r="H39" s="12">
+        <v>108861896</v>
+      </c>
+      <c r="I39" s="26"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="27">
+        <v>192</v>
+      </c>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="13"/>
+    </row>
+    <row r="40" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="10">
+        <v>39</v>
+      </c>
+      <c r="B40" s="10">
         <v>995</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0.72593750000000001</v>
-      </c>
-      <c r="E11" s="12" t="s">
+      <c r="C40" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="11">
+        <v>0.35880787037037037</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F40" s="12">
+        <v>8099000</v>
+      </c>
+      <c r="G40" s="10">
+        <v>0</v>
+      </c>
+      <c r="H40" s="12">
+        <v>100762896</v>
+      </c>
+      <c r="I40" s="26"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="10">
+        <v>40</v>
+      </c>
+      <c r="B41" s="10">
+        <v>995</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="11">
+        <v>0.37584490740740739</v>
+      </c>
+      <c r="E41" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="24">
-        <v>18600</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0</v>
-      </c>
-      <c r="H11" s="14">
-        <v>60365436</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="23">
+      <c r="F41" s="22">
+        <v>28200</v>
+      </c>
+      <c r="G41" s="10">
+        <v>0</v>
+      </c>
+      <c r="H41" s="12">
+        <v>100734696</v>
+      </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="21">
         <v>223</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N41" s="21">
         <v>291</v>
       </c>
-      <c r="O11" s="23">
-        <v>18600</v>
-      </c>
-      <c r="P11" s="15" t="s">
+      <c r="O41" s="21">
+        <v>28200</v>
+      </c>
+      <c r="P41" s="13" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12">
+    <row r="42" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="10">
+        <v>41</v>
+      </c>
+      <c r="B42" s="10">
         <v>995</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="13">
-        <v>0.72593750000000001</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="14">
-        <v>39318600</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="14">
-        <v>21046836</v>
-      </c>
-      <c r="I12" s="23">
-        <v>231</v>
-      </c>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="23">
-        <v>298</v>
-      </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="12">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="C42" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="11">
+        <v>0.37584490740740739</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="12">
+        <v>66200000</v>
+      </c>
+      <c r="G42" s="10">
+        <v>0</v>
+      </c>
+      <c r="H42" s="12">
+        <v>34534696</v>
+      </c>
+      <c r="I42" s="26"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="10"/>
+      <c r="B43" s="10">
         <v>995</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0.78163194444444439</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="24">
-        <v>9000</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14">
-        <v>21037836</v>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="23">
-        <v>223</v>
-      </c>
-      <c r="N13" s="23">
-        <v>291</v>
-      </c>
-      <c r="O13" s="23">
-        <v>9000</v>
-      </c>
-      <c r="P13" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="12">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12">
-        <v>995</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="13">
-        <v>0.78163194444444439</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="14">
-        <v>4000000</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0</v>
-      </c>
-      <c r="H14" s="14">
-        <v>17037836</v>
-      </c>
-      <c r="I14" s="23">
-        <v>230</v>
-      </c>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="23">
-        <v>297</v>
-      </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="12">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12">
-        <v>995</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="13">
-        <v>0.81062500000000004</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="12">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
-        <v>21275000</v>
-      </c>
-      <c r="H15" s="14">
-        <v>38312836</v>
-      </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="15"/>
-    </row>
-    <row r="16" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="12">
-        <v>15</v>
-      </c>
-      <c r="B16" s="12">
-        <v>995</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="13">
-        <v>0.4157986111111111</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="14">
-        <v>2756000</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>35556836</v>
-      </c>
-      <c r="I16" s="23">
-        <v>232</v>
-      </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="23">
-        <v>299</v>
-      </c>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="12">
-        <v>16</v>
-      </c>
-      <c r="B17" s="12">
-        <v>995</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="13">
-        <v>0.42410879629629628</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="14">
-        <v>1400000</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0</v>
-      </c>
-      <c r="H17" s="14">
-        <v>34156836</v>
-      </c>
-      <c r="I17" s="23">
-        <v>233</v>
-      </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="23">
-        <v>300</v>
-      </c>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="12">
-        <v>17</v>
-      </c>
-      <c r="B18" s="12">
-        <v>1</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0.59675925925925921</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="12">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14">
-        <v>100000000</v>
-      </c>
-      <c r="H18" s="14">
-        <v>134156836</v>
-      </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="15"/>
-    </row>
-    <row r="19" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="12">
-        <v>18</v>
-      </c>
-      <c r="B19" s="12">
-        <v>995</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0.45131944444444444</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="24">
-        <v>9000</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0</v>
-      </c>
-      <c r="H19" s="14">
-        <v>134147836</v>
-      </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="23">
-        <v>223</v>
-      </c>
-      <c r="N19" s="23">
-        <v>291</v>
-      </c>
-      <c r="O19" s="23">
-        <v>9000</v>
-      </c>
-      <c r="P19" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="12">
-        <v>19</v>
-      </c>
-      <c r="B20" s="12">
-        <v>995</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="13">
-        <v>0.45131944444444444</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="14">
-        <v>1430000</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>132717836</v>
-      </c>
-      <c r="I20" s="23">
-        <v>234</v>
-      </c>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="23">
-        <v>301</v>
-      </c>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="12">
-        <v>20</v>
-      </c>
-      <c r="B21" s="12">
-        <v>995</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0.45287037037037037</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="24">
-        <v>28200</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14">
-        <v>132689636</v>
-      </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="23">
-        <v>223</v>
-      </c>
-      <c r="N21" s="23">
-        <v>291</v>
-      </c>
-      <c r="O21" s="23">
-        <v>28200</v>
-      </c>
-      <c r="P21" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="12">
-        <v>21</v>
-      </c>
-      <c r="B22" s="12">
-        <v>995</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="13">
-        <v>0.45287037037037037</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" s="14">
-        <v>64500000</v>
-      </c>
-      <c r="G22" s="12">
-        <v>0</v>
-      </c>
-      <c r="H22" s="14">
-        <v>68189636</v>
-      </c>
-      <c r="I22" s="23">
-        <v>235</v>
-      </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="23">
-        <v>302</v>
-      </c>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="12">
-        <v>22</v>
-      </c>
-      <c r="B23" s="12">
-        <v>995</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="13">
-        <v>0.46592592592592591</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="14">
-        <v>105000</v>
-      </c>
-      <c r="G23" s="12">
-        <v>0</v>
-      </c>
-      <c r="H23" s="14">
-        <v>68084636</v>
-      </c>
-      <c r="I23" s="23">
-        <v>236</v>
-      </c>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="23">
-        <v>303</v>
-      </c>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="12">
-        <v>23</v>
-      </c>
-      <c r="B24" s="12">
-        <v>995</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="13">
-        <v>0.58806712962962959</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="14">
-        <v>3100000</v>
-      </c>
-      <c r="G24" s="12">
-        <v>0</v>
-      </c>
-      <c r="H24" s="14">
-        <v>64984636</v>
-      </c>
-      <c r="I24" s="23">
-        <v>237</v>
-      </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="23">
-        <v>304</v>
-      </c>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="12">
-        <v>24</v>
-      </c>
-      <c r="B25" s="12">
-        <v>995</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="13">
-        <v>0.46016203703703706</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="14">
-        <v>13000000</v>
-      </c>
-      <c r="G25" s="12">
-        <v>0</v>
-      </c>
-      <c r="H25" s="14">
-        <v>51984636</v>
-      </c>
-      <c r="I25" s="23"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="12">
-        <v>25</v>
-      </c>
-      <c r="B26" s="12">
-        <v>995</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="13">
-        <v>0.73033564814814811</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="14">
-        <v>2756000</v>
-      </c>
-      <c r="G26" s="12">
-        <v>0</v>
-      </c>
-      <c r="H26" s="14">
-        <v>49228636</v>
-      </c>
-      <c r="I26" s="23">
-        <v>232</v>
-      </c>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="23">
-        <v>299</v>
-      </c>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="12">
-        <v>26</v>
-      </c>
-      <c r="B27" s="12">
-        <v>1</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="13">
-        <v>0.5465740740740741</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" s="12">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14">
-        <v>100000000</v>
-      </c>
-      <c r="H27" s="14">
-        <v>149228636</v>
-      </c>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="15"/>
-    </row>
-    <row r="28" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="12">
-        <v>27</v>
-      </c>
-      <c r="B28" s="12">
-        <v>995</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="13">
-        <v>0.42841435185185184</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="14">
-        <v>16520000</v>
-      </c>
-      <c r="G28" s="12">
-        <v>0</v>
-      </c>
-      <c r="H28" s="14">
-        <v>132708636</v>
-      </c>
-      <c r="I28" s="23">
-        <v>228</v>
-      </c>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="23">
-        <v>296</v>
-      </c>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="12">
-        <v>28</v>
-      </c>
-      <c r="B29" s="12">
-        <v>995</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="13">
-        <v>0.71627314814814813</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2756000</v>
-      </c>
-      <c r="G29" s="12">
-        <v>0</v>
-      </c>
-      <c r="H29" s="14">
-        <v>129952636</v>
-      </c>
-      <c r="I29" s="23">
-        <v>232</v>
-      </c>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="23">
-        <v>299</v>
-      </c>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="19">
-        <v>29</v>
-      </c>
-      <c r="B30" s="19">
-        <v>995</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="20">
-        <v>0.71671296296296294</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" s="21">
-        <v>2756000</v>
-      </c>
-      <c r="G30" s="19">
-        <v>0</v>
-      </c>
-      <c r="H30" s="21">
-        <v>127196636</v>
-      </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="22" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="19">
-        <v>30</v>
-      </c>
-      <c r="B31" s="19">
-        <v>995</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" s="20">
-        <v>0.71753472222222225</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F31" s="19">
-        <v>0</v>
-      </c>
-      <c r="G31" s="21">
-        <v>2756000</v>
-      </c>
-      <c r="H31" s="21">
-        <v>129952636</v>
-      </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="22" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="12">
-        <v>31</v>
-      </c>
-      <c r="B32" s="12">
-        <v>995</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="13">
-        <v>0.39391203703703703</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="24">
-        <v>31400</v>
-      </c>
-      <c r="G32" s="12">
-        <v>0</v>
-      </c>
-      <c r="H32" s="14">
-        <v>129921236</v>
-      </c>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="23">
-        <v>223</v>
-      </c>
-      <c r="N32" s="23">
-        <v>291</v>
-      </c>
-      <c r="O32" s="23">
-        <v>31400</v>
-      </c>
-      <c r="P32" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="12">
-        <v>32</v>
-      </c>
-      <c r="B33" s="12">
-        <v>995</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="13">
-        <v>0.39391203703703703</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="14">
-        <v>80000000</v>
-      </c>
-      <c r="G33" s="12">
-        <v>0</v>
-      </c>
-      <c r="H33" s="14">
-        <v>49921236</v>
-      </c>
-      <c r="I33" s="23"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="12">
-        <v>33</v>
-      </c>
-      <c r="B34" s="12">
-        <v>10</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" s="13">
-        <v>0.38908564814814817</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34" s="14">
-        <v>50340</v>
-      </c>
-      <c r="G34" s="12">
-        <v>0</v>
-      </c>
-      <c r="H34" s="14">
-        <v>49870896</v>
-      </c>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="23">
-        <v>223</v>
-      </c>
-      <c r="N34" s="23">
-        <v>291</v>
-      </c>
-      <c r="O34" s="23">
-        <v>50340</v>
-      </c>
-      <c r="P34" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="12">
-        <v>34</v>
-      </c>
-      <c r="B35" s="12">
-        <v>995</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="13">
-        <v>0.39223379629629629</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" s="14">
-        <v>3500000</v>
-      </c>
-      <c r="G35" s="12">
-        <v>0</v>
-      </c>
-      <c r="H35" s="14">
-        <v>46370896</v>
-      </c>
-      <c r="I35" s="23"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="15" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="12">
-        <v>35</v>
-      </c>
-      <c r="B36" s="12">
-        <v>995</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" s="13">
-        <v>0.77943287037037035</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" s="24">
-        <v>9000</v>
-      </c>
-      <c r="G36" s="12">
-        <v>0</v>
-      </c>
-      <c r="H36" s="14">
-        <v>46361896</v>
-      </c>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="23">
-        <v>223</v>
-      </c>
-      <c r="N36" s="23">
-        <v>291</v>
-      </c>
-      <c r="O36" s="23">
-        <v>9000</v>
-      </c>
-      <c r="P36" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="12">
-        <v>36</v>
-      </c>
-      <c r="B37" s="12">
-        <v>995</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="13">
-        <v>0.77943287037037035</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F37" s="14">
-        <v>4000000</v>
-      </c>
-      <c r="G37" s="12">
-        <v>0</v>
-      </c>
-      <c r="H37" s="14">
-        <v>42361896</v>
-      </c>
-      <c r="I37" s="23">
-        <v>230</v>
-      </c>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="23">
-        <v>297</v>
-      </c>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="12"/>
-      <c r="P37" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="12">
-        <v>37</v>
-      </c>
-      <c r="B38" s="12">
-        <v>995</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="13">
-        <v>0.81400462962962961</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38" s="14">
-        <v>21500000</v>
-      </c>
-      <c r="G38" s="12">
-        <v>0</v>
-      </c>
-      <c r="H38" s="14">
-        <v>20861896</v>
-      </c>
-      <c r="I38" s="23">
-        <v>229</v>
-      </c>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="23">
-        <v>296</v>
-      </c>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="12"/>
-      <c r="P38" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="12">
-        <v>38</v>
-      </c>
-      <c r="B39" s="12">
-        <v>1</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" s="13">
-        <v>0.46181712962962962</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F39" s="12">
-        <v>0</v>
-      </c>
-      <c r="G39" s="14">
-        <v>88000000</v>
-      </c>
-      <c r="H39" s="14">
-        <v>108861896</v>
-      </c>
-      <c r="I39" s="23"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="12"/>
-      <c r="P39" s="15"/>
-    </row>
-    <row r="40" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="12">
-        <v>39</v>
-      </c>
-      <c r="B40" s="12">
-        <v>995</v>
-      </c>
-      <c r="C40" s="12" t="s">
+      <c r="C43" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="13">
-        <v>0.35880787037037037</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="F40" s="14">
-        <v>8099000</v>
-      </c>
-      <c r="G40" s="12">
-        <v>0</v>
-      </c>
-      <c r="H40" s="14">
-        <v>100762896</v>
-      </c>
-      <c r="I40" s="23"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="12"/>
-      <c r="P40" s="15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="12">
-        <v>40</v>
-      </c>
-      <c r="B41" s="12">
-        <v>995</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="13">
-        <v>0.37584490740740739</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="24">
-        <v>28200</v>
-      </c>
-      <c r="G41" s="12">
-        <v>0</v>
-      </c>
-      <c r="H41" s="14">
-        <v>100734696</v>
-      </c>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
-      <c r="M41" s="23">
-        <v>223</v>
-      </c>
-      <c r="N41" s="23">
-        <v>291</v>
-      </c>
-      <c r="O41" s="23">
-        <v>28200</v>
-      </c>
-      <c r="P41" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="12">
-        <v>41</v>
-      </c>
-      <c r="B42" s="12">
-        <v>995</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="13">
-        <v>0.37584490740740739</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="F42" s="14">
-        <v>66200000</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0</v>
-      </c>
-      <c r="H42" s="14">
-        <v>34534696</v>
-      </c>
-      <c r="I42" s="23"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="12"/>
-      <c r="P42" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12">
-        <v>995</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" s="13">
+      <c r="D43" s="11">
         <v>0.42988425925925927</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="14">
+      <c r="F43" s="12">
         <v>559000</v>
       </c>
-      <c r="G43" s="12">
-        <v>0</v>
-      </c>
-      <c r="H43" s="14">
+      <c r="G43" s="10">
+        <v>0</v>
+      </c>
+      <c r="H43" s="12">
         <v>33975696</v>
       </c>
-      <c r="I43" s="23"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="12"/>
-      <c r="P43" s="15" t="s">
+      <c r="I43" s="26"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="13" t="s">
         <v>123</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P43" xr:uid="{19177F00-A1E8-448E-8485-489AD9D9EC23}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P43">
+    <sortCondition ref="A1:A43"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/Invoice_10.11651202.1_1405_05_26.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/Invoice_10.11651202.1_1405_05_26.xlsx
@@ -526,7 +526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -596,59 +596,23 @@
     <xf numFmtId="3" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF7030A0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF7030A0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -994,30 +958,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -2267,17 +2231,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3304,10 +3268,10 @@
       <c r="H25" s="12">
         <v>51984636</v>
       </c>
-      <c r="I25" s="26"/>
+      <c r="I25" s="23"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="26"/>
+      <c r="L25" s="23"/>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
@@ -3610,10 +3574,10 @@
       <c r="H33" s="12">
         <v>49921236</v>
       </c>
-      <c r="I33" s="26"/>
+      <c r="I33" s="23"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="26"/>
+      <c r="L33" s="23"/>
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
       <c r="O33" s="10"/>
@@ -3688,10 +3652,10 @@
       <c r="H35" s="12">
         <v>46370896</v>
       </c>
-      <c r="I35" s="26"/>
+      <c r="I35" s="23"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="26"/>
+      <c r="L35" s="23"/>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
       <c r="O35" s="10"/>
@@ -3846,9 +3810,9 @@
       <c r="H39" s="12">
         <v>108861896</v>
       </c>
-      <c r="I39" s="26"/>
+      <c r="I39" s="23"/>
       <c r="J39" s="10"/>
-      <c r="K39" s="27">
+      <c r="K39" s="24">
         <v>192</v>
       </c>
       <c r="L39" s="10"/>
@@ -3882,10 +3846,10 @@
       <c r="H40" s="12">
         <v>100762896</v>
       </c>
-      <c r="I40" s="26"/>
+      <c r="I40" s="23"/>
       <c r="J40" s="10"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="26"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="23"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
       <c r="O40" s="10"/>
@@ -3960,10 +3924,10 @@
       <c r="H42" s="12">
         <v>34534696</v>
       </c>
-      <c r="I42" s="26"/>
+      <c r="I42" s="23"/>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
-      <c r="L42" s="26"/>
+      <c r="L42" s="23"/>
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
       <c r="O42" s="10"/>
@@ -3994,10 +3958,10 @@
       <c r="H43" s="12">
         <v>33975696</v>
       </c>
-      <c r="I43" s="26"/>
+      <c r="I43" s="23"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
-      <c r="L43" s="26"/>
+      <c r="L43" s="23"/>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
       <c r="O43" s="10"/>
